--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N87_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N87_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.98081097395158</v>
+        <v>5.196881783267132</v>
       </c>
       <c r="D2" t="n">
-        <v>18.0033563366457</v>
+        <v>2.925545404704927</v>
       </c>
       <c r="E2" t="n">
-        <v>9.430708329755923</v>
+        <v>1.532490103585337</v>
       </c>
       <c r="F2" t="n">
-        <v>15.92714933719947</v>
+        <v>2.588161767294914</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.74958299018915</v>
+        <v>7.759307235905737</v>
       </c>
       <c r="D3" t="n">
-        <v>39.23170575072044</v>
+        <v>6.375152184492071</v>
       </c>
       <c r="E3" t="n">
-        <v>9.430708329755923</v>
+        <v>1.532490103585337</v>
       </c>
       <c r="F3" t="n">
-        <v>15.92714933719947</v>
+        <v>2.588161767294914</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.68299009439497</v>
+        <v>4.010985890339183</v>
       </c>
       <c r="D4" t="n">
-        <v>31.13773662255027</v>
+        <v>5.059882201164418</v>
       </c>
       <c r="E4" t="n">
-        <v>9.430708329755923</v>
+        <v>1.532490103585337</v>
       </c>
       <c r="F4" t="n">
-        <v>15.92714933719947</v>
+        <v>2.588161767294914</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.62214450449026</v>
+        <v>4.001098481979668</v>
       </c>
       <c r="D5" t="n">
-        <v>61.81272577570387</v>
+        <v>10.04456793855188</v>
       </c>
       <c r="E5" t="n">
-        <v>9.430708329755923</v>
+        <v>1.532490103585337</v>
       </c>
       <c r="F5" t="n">
-        <v>15.92714933719947</v>
+        <v>2.588161767294914</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
